--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DFS_HRM-2031-0332/Panel 7/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DFS_HRM-2031-0332/Panel 7/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,17 +434,17 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -456,26 +456,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.57183</v>
+        <v>16.78252</v>
       </c>
       <c r="D2" t="n">
-        <v>15.99016</v>
+        <v>16.5696</v>
       </c>
       <c r="E2" t="n">
-        <v>16.30253</v>
+        <v>16.75113</v>
       </c>
       <c r="F2" t="n">
-        <v>22.17563</v>
+        <v>42.44395</v>
       </c>
       <c r="G2" t="n">
-        <v>21.43368</v>
+        <v>0.0496</v>
       </c>
       <c r="H2" t="n">
-        <v>33.87582</v>
+        <v>1.83243</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.7491</v>
+        <v>16.8936</v>
       </c>
       <c r="D3" t="n">
-        <v>15.9878</v>
+        <v>16.4352</v>
       </c>
       <c r="E3" t="n">
-        <v>16.2415</v>
+        <v>16.80516</v>
       </c>
       <c r="F3" t="n">
-        <v>22.04798</v>
+        <v>41.72725</v>
       </c>
       <c r="G3" t="n">
-        <v>21.64784</v>
+        <v>0.05052</v>
       </c>
       <c r="H3" t="n">
-        <v>34.37174</v>
+        <v>1.84425</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.84854</v>
+        <v>16.89468</v>
       </c>
       <c r="D4" t="n">
-        <v>15.95772</v>
+        <v>16.47073</v>
       </c>
       <c r="E4" t="n">
-        <v>16.07537</v>
+        <v>16.64326</v>
       </c>
       <c r="F4" t="n">
-        <v>21.89228</v>
+        <v>43.23168</v>
       </c>
       <c r="G4" t="n">
-        <v>22.21499</v>
+        <v>0.05104</v>
       </c>
       <c r="H4" t="n">
-        <v>34.4125</v>
+        <v>1.79516</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.58875</v>
+        <v>16.81529</v>
       </c>
       <c r="D5" t="n">
-        <v>15.8418</v>
+        <v>16.46901</v>
       </c>
       <c r="E5" t="n">
-        <v>16.40332</v>
+        <v>16.54969</v>
       </c>
       <c r="F5" t="n">
-        <v>21.6017</v>
+        <v>42.33823</v>
       </c>
       <c r="G5" t="n">
-        <v>21.88924</v>
+        <v>0.05023</v>
       </c>
       <c r="H5" t="n">
-        <v>34.14975</v>
+        <v>1.76797</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.69902</v>
+        <v>16.604</v>
       </c>
       <c r="D6" t="n">
-        <v>16.12033</v>
+        <v>16.49797</v>
       </c>
       <c r="E6" t="n">
-        <v>16.49052</v>
+        <v>16.58723</v>
       </c>
       <c r="F6" t="n">
-        <v>21.81258</v>
+        <v>41.82081</v>
       </c>
       <c r="G6" t="n">
-        <v>21.48474</v>
+        <v>0.05071</v>
       </c>
       <c r="H6" t="n">
-        <v>34.52248</v>
+        <v>1.79365</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.67914</v>
+        <v>16.65303</v>
       </c>
       <c r="D7" t="n">
-        <v>15.95529</v>
+        <v>16.59408</v>
       </c>
       <c r="E7" t="n">
-        <v>16.28819</v>
+        <v>16.63209</v>
       </c>
       <c r="F7" t="n">
-        <v>21.38922</v>
+        <v>42.46251</v>
       </c>
       <c r="G7" t="n">
-        <v>21.68773</v>
+        <v>0.05104</v>
       </c>
       <c r="H7" t="n">
-        <v>34.03355</v>
+        <v>1.80949</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.34606</v>
+        <v>16.96324</v>
       </c>
       <c r="D8" t="n">
-        <v>15.65406</v>
+        <v>16.43413</v>
       </c>
       <c r="E8" t="n">
-        <v>16.21648</v>
+        <v>16.94741</v>
       </c>
       <c r="F8" t="n">
-        <v>21.41759</v>
+        <v>41.76579</v>
       </c>
       <c r="G8" t="n">
-        <v>21.23454</v>
+        <v>0.0514</v>
       </c>
       <c r="H8" t="n">
-        <v>33.22276</v>
+        <v>1.82451</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.39965</v>
+        <v>16.69602</v>
       </c>
       <c r="D9" t="n">
-        <v>16.0074</v>
+        <v>16.64704</v>
       </c>
       <c r="E9" t="n">
-        <v>16.27077</v>
+        <v>16.68441</v>
       </c>
       <c r="F9" t="n">
-        <v>21.97368</v>
+        <v>42.78909</v>
       </c>
       <c r="G9" t="n">
-        <v>21.60864</v>
+        <v>0.0488</v>
       </c>
       <c r="H9" t="n">
-        <v>33.9173</v>
+        <v>1.83715</v>
       </c>
     </row>
     <row r="10">
@@ -660,63 +660,53 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.69404</v>
+        <v>16.84261</v>
       </c>
       <c r="D10" t="n">
-        <v>15.81057</v>
+        <v>16.60361</v>
       </c>
       <c r="E10" t="n">
-        <v>16.01604</v>
+        <v>16.68041</v>
       </c>
       <c r="F10" t="n">
-        <v>21.46514</v>
+        <v>42.38112</v>
       </c>
       <c r="G10" t="n">
-        <v>21.59748</v>
+        <v>0.04992</v>
       </c>
       <c r="H10" t="n">
-        <v>34.37735</v>
+        <v>1.80272</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Rz mean</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rz min</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ra mean</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Ra max</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -728,32 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>roughness</t>
+          <t>Pad 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.73714</v>
+        <v>17.03091</v>
       </c>
       <c r="D12" t="n">
-        <v>0.08075</v>
+        <v>16.29411</v>
       </c>
       <c r="E12" t="n">
-        <v>0.59944</v>
+        <v>16.60649</v>
       </c>
       <c r="F12" t="n">
-        <v>0.96407</v>
+        <v>42.56018</v>
       </c>
       <c r="G12" t="n">
-        <v>0.10978</v>
+        <v>0.0495</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00748</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.0912</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.12494</v>
+        <v>1.82447</v>
       </c>
     </row>
     <row r="13">
@@ -763,28 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.74127</v>
+        <v>16.57711</v>
       </c>
       <c r="D13" t="n">
-        <v>0.07998</v>
+        <v>16.14461</v>
       </c>
       <c r="E13" t="n">
-        <v>0.60025</v>
+        <v>16.51679</v>
       </c>
       <c r="F13" t="n">
-        <v>0.98076</v>
+        <v>42.3242</v>
       </c>
       <c r="G13" t="n">
-        <v>0.10748</v>
+        <v>0.05023</v>
       </c>
       <c r="H13" t="n">
-        <v>0.00748</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.09376</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.12443</v>
+        <v>1.84614</v>
       </c>
     </row>
     <row r="14">
@@ -794,28 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.76044</v>
+        <v>16.56396</v>
       </c>
       <c r="D14" t="n">
-        <v>0.08094</v>
+        <v>16.39431</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6097399999999999</v>
+        <v>16.55496</v>
       </c>
       <c r="F14" t="n">
-        <v>0.96114</v>
+        <v>42.27868</v>
       </c>
       <c r="G14" t="n">
-        <v>0.11051</v>
+        <v>0.05004</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00746</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.09385</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.12362</v>
+        <v>1.81345</v>
       </c>
     </row>
     <row r="15">
@@ -825,28 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.7501</v>
+        <v>16.82177</v>
       </c>
       <c r="D15" t="n">
-        <v>0.08087</v>
+        <v>16.35535</v>
       </c>
       <c r="E15" t="n">
-        <v>0.60243</v>
+        <v>16.42373</v>
       </c>
       <c r="F15" t="n">
-        <v>0.95314</v>
+        <v>42.62235</v>
       </c>
       <c r="G15" t="n">
-        <v>0.10861</v>
+        <v>0.05021</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00757</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.09352000000000001</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.12501</v>
+        <v>1.79906</v>
       </c>
     </row>
     <row r="16">
@@ -856,28 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.75543</v>
+        <v>16.84015</v>
       </c>
       <c r="D16" t="n">
-        <v>0.08008</v>
+        <v>16.69596</v>
       </c>
       <c r="E16" t="n">
-        <v>0.58995</v>
+        <v>16.71868</v>
       </c>
       <c r="F16" t="n">
-        <v>0.92601</v>
+        <v>42.69407</v>
       </c>
       <c r="G16" t="n">
-        <v>0.10863</v>
+        <v>0.05041</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.09377000000000001</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.12498</v>
+        <v>1.80801</v>
       </c>
     </row>
     <row r="17">
@@ -887,28 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.7521600000000001</v>
+        <v>16.94019</v>
       </c>
       <c r="D17" t="n">
-        <v>0.07987</v>
+        <v>16.43265</v>
       </c>
       <c r="E17" t="n">
-        <v>0.60203</v>
+        <v>16.77677</v>
       </c>
       <c r="F17" t="n">
-        <v>0.95452</v>
+        <v>42.32391</v>
       </c>
       <c r="G17" t="n">
-        <v>0.10792</v>
+        <v>0.04981</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00758</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.09462</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.12631</v>
+        <v>1.81509</v>
       </c>
     </row>
     <row r="18">
@@ -918,28 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.74239</v>
+        <v>16.89473</v>
       </c>
       <c r="D18" t="n">
-        <v>0.08066</v>
+        <v>16.00911</v>
       </c>
       <c r="E18" t="n">
-        <v>0.59557</v>
+        <v>16.30387</v>
       </c>
       <c r="F18" t="n">
-        <v>0.95043</v>
+        <v>42.00245</v>
       </c>
       <c r="G18" t="n">
-        <v>0.10786</v>
+        <v>0.04944</v>
       </c>
       <c r="H18" t="n">
-        <v>0.00745</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.09384000000000001</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.12739</v>
+        <v>1.78624</v>
       </c>
     </row>
     <row r="19">
@@ -949,28 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.74556</v>
+        <v>16.94003</v>
       </c>
       <c r="D19" t="n">
-        <v>0.07938000000000001</v>
+        <v>16.49546</v>
       </c>
       <c r="E19" t="n">
-        <v>0.61328</v>
+        <v>16.8148</v>
       </c>
       <c r="F19" t="n">
-        <v>0.93615</v>
+        <v>42.44214</v>
       </c>
       <c r="G19" t="n">
-        <v>0.10726</v>
+        <v>0.05031</v>
       </c>
       <c r="H19" t="n">
-        <v>0.00742</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.09501999999999999</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.12452</v>
+        <v>1.82269</v>
       </c>
     </row>
     <row r="20">
@@ -980,28 +922,1274 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.74017</v>
+        <v>16.80353</v>
       </c>
       <c r="D20" t="n">
-        <v>0.08101</v>
+        <v>16.22929</v>
       </c>
       <c r="E20" t="n">
-        <v>0.61587</v>
+        <v>16.67159</v>
       </c>
       <c r="F20" t="n">
-        <v>0.97636</v>
+        <v>42.95769</v>
       </c>
       <c r="G20" t="n">
-        <v>0.10829</v>
+        <v>0.0513</v>
       </c>
       <c r="H20" t="n">
+        <v>1.785</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SR Pad 1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>15.96379</v>
+      </c>
+      <c r="D22" t="n">
+        <v>15.38831</v>
+      </c>
+      <c r="E22" t="n">
+        <v>15.55921</v>
+      </c>
+      <c r="F22" t="n">
+        <v>254.06974</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>15.73652</v>
+      </c>
+      <c r="D23" t="n">
+        <v>15.29028</v>
+      </c>
+      <c r="E23" t="n">
+        <v>15.35445</v>
+      </c>
+      <c r="F23" t="n">
+        <v>251.72815</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>15.84685</v>
+      </c>
+      <c r="D24" t="n">
+        <v>15.38011</v>
+      </c>
+      <c r="E24" t="n">
+        <v>15.48449</v>
+      </c>
+      <c r="F24" t="n">
+        <v>256.97272</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>15.70398</v>
+      </c>
+      <c r="D25" t="n">
+        <v>15.42598</v>
+      </c>
+      <c r="E25" t="n">
+        <v>15.63528</v>
+      </c>
+      <c r="F25" t="n">
+        <v>248.8366</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>15.83086</v>
+      </c>
+      <c r="D26" t="n">
+        <v>15.21034</v>
+      </c>
+      <c r="E26" t="n">
+        <v>15.42646</v>
+      </c>
+      <c r="F26" t="n">
+        <v>255.73782</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>15.52708</v>
+      </c>
+      <c r="D27" t="n">
+        <v>15.16335</v>
+      </c>
+      <c r="E27" t="n">
+        <v>15.37882</v>
+      </c>
+      <c r="F27" t="n">
+        <v>250.7988</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>15.71892</v>
+      </c>
+      <c r="D28" t="n">
+        <v>15.41847</v>
+      </c>
+      <c r="E28" t="n">
+        <v>15.60392</v>
+      </c>
+      <c r="F28" t="n">
+        <v>259.99609</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>15.60863</v>
+      </c>
+      <c r="D29" t="n">
+        <v>15.56991</v>
+      </c>
+      <c r="E29" t="n">
+        <v>15.58385</v>
+      </c>
+      <c r="F29" t="n">
+        <v>255.95031</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>15.76357</v>
+      </c>
+      <c r="D30" t="n">
+        <v>15.41601</v>
+      </c>
+      <c r="E30" t="n">
+        <v>15.56878</v>
+      </c>
+      <c r="F30" t="n">
+        <v>248.72968</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>16.37289</v>
+      </c>
+      <c r="D32" t="n">
+        <v>15.86537</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.13628</v>
+      </c>
+      <c r="F32" t="n">
+        <v>21.31171</v>
+      </c>
+      <c r="G32" t="n">
+        <v>34.10896</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>16.44309</v>
+      </c>
+      <c r="D33" t="n">
+        <v>15.85542</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16.03835</v>
+      </c>
+      <c r="F33" t="n">
+        <v>21.71886</v>
+      </c>
+      <c r="G33" t="n">
+        <v>33.68669</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>16.75946</v>
+      </c>
+      <c r="D34" t="n">
+        <v>16.00908</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16.01739</v>
+      </c>
+      <c r="F34" t="n">
+        <v>21.61342</v>
+      </c>
+      <c r="G34" t="n">
+        <v>33.82812</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>16.53494</v>
+      </c>
+      <c r="D35" t="n">
+        <v>16.15083</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.25255</v>
+      </c>
+      <c r="F35" t="n">
+        <v>21.72862</v>
+      </c>
+      <c r="G35" t="n">
+        <v>34.22916</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>17.01131</v>
+      </c>
+      <c r="D36" t="n">
+        <v>15.63437</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16.36003</v>
+      </c>
+      <c r="F36" t="n">
+        <v>21.90747</v>
+      </c>
+      <c r="G36" t="n">
+        <v>34.12856</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>16.94656</v>
+      </c>
+      <c r="D37" t="n">
+        <v>15.78184</v>
+      </c>
+      <c r="E37" t="n">
+        <v>16.57787</v>
+      </c>
+      <c r="F37" t="n">
+        <v>22.04289</v>
+      </c>
+      <c r="G37" t="n">
+        <v>33.94274</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>16.95064</v>
+      </c>
+      <c r="D38" t="n">
+        <v>16.02817</v>
+      </c>
+      <c r="E38" t="n">
+        <v>16.42181</v>
+      </c>
+      <c r="F38" t="n">
+        <v>21.62789</v>
+      </c>
+      <c r="G38" t="n">
+        <v>33.67654</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16.55295</v>
+      </c>
+      <c r="D39" t="n">
+        <v>15.89125</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.53527</v>
+      </c>
+      <c r="F39" t="n">
+        <v>21.37294</v>
+      </c>
+      <c r="G39" t="n">
+        <v>33.5411</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>16.4926</v>
+      </c>
+      <c r="D40" t="n">
+        <v>15.8785</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.01251</v>
+      </c>
+      <c r="F40" t="n">
+        <v>21.17111</v>
+      </c>
+      <c r="G40" t="n">
+        <v>34.81952</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Trace 2</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>16.75558</v>
+      </c>
+      <c r="D42" t="n">
+        <v>15.91328</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.21783</v>
+      </c>
+      <c r="F42" t="n">
+        <v>21.55971</v>
+      </c>
+      <c r="G42" t="n">
+        <v>34.63513</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>16.66176</v>
+      </c>
+      <c r="D43" t="n">
+        <v>15.94417</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.00051</v>
+      </c>
+      <c r="F43" t="n">
+        <v>21.76427</v>
+      </c>
+      <c r="G43" t="n">
+        <v>33.93565</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>16.83063</v>
+      </c>
+      <c r="D44" t="n">
+        <v>16.05528</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.3157</v>
+      </c>
+      <c r="F44" t="n">
+        <v>21.55262</v>
+      </c>
+      <c r="G44" t="n">
+        <v>33.75073</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>16.8369</v>
+      </c>
+      <c r="D45" t="n">
+        <v>15.88343</v>
+      </c>
+      <c r="E45" t="n">
+        <v>16.16997</v>
+      </c>
+      <c r="F45" t="n">
+        <v>21.64681</v>
+      </c>
+      <c r="G45" t="n">
+        <v>34.01812</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>16.79247</v>
+      </c>
+      <c r="D46" t="n">
+        <v>15.71653</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.46323</v>
+      </c>
+      <c r="F46" t="n">
+        <v>21.76878</v>
+      </c>
+      <c r="G46" t="n">
+        <v>33.48991</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>16.63358</v>
+      </c>
+      <c r="D47" t="n">
+        <v>15.66939</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.42428</v>
+      </c>
+      <c r="F47" t="n">
+        <v>21.33254</v>
+      </c>
+      <c r="G47" t="n">
+        <v>33.92946</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>16.45517</v>
+      </c>
+      <c r="D48" t="n">
+        <v>15.7956</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.10685</v>
+      </c>
+      <c r="F48" t="n">
+        <v>21.46942</v>
+      </c>
+      <c r="G48" t="n">
+        <v>33.83812</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>16.80613</v>
+      </c>
+      <c r="D49" t="n">
+        <v>15.80825</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16.44112</v>
+      </c>
+      <c r="F49" t="n">
+        <v>21.45283</v>
+      </c>
+      <c r="G49" t="n">
+        <v>34.12744</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>16.48382</v>
+      </c>
+      <c r="D50" t="n">
+        <v>15.88344</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.14132</v>
+      </c>
+      <c r="F50" t="n">
+        <v>21.35985</v>
+      </c>
+      <c r="G50" t="n">
+        <v>33.76912</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.61834</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.09109</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.59959</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.11764</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.6140600000000001</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.11201</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.60654</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.09557</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.60018</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.10143</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.59018</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.09429</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.60639</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.11978</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.59155</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.08244</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.6008599999999999</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.11124</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>via 2</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.60593</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.11313</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.61594</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.09861</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.61015</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.11089</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.60653</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.10572</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.59021</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1.07585</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.61108</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.12626</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.61353</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.1115</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.6006899999999999</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.1007</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.60199</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.07806</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0.73653</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.07932</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.60333</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.97338</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.10681</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.00767</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.09215</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.12547</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0.72917</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.08354</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.61519</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.95096</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.10585</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.00744</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.09257</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.12392</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0.73212</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.08180999999999999</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.59399</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.94248</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.10753</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.00748</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.0924</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.12469</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.75232</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.08205</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.60477</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.95802</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.10778</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.00745</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.09188</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.12708</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0.73487</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.07994999999999999</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.60283</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.9695</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.10873</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.00757</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.09189</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.12811</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.7571</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.08103</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.5992499999999999</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.96854</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.10781</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.00754</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.09374</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.12744</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0.76555</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.08069999999999999</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.60421</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.95967</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.1089</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.00759</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.09141000000000001</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.12516</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0.75671</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.08116</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.6161</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.95357</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.10803</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.00764</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.09130000000000001</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.12375</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0.73775</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.07994</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.59275</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.9589</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.1106</v>
+      </c>
+      <c r="H80" t="n">
         <v>0.00765</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.09131</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.12382</v>
+      <c r="I80" t="n">
+        <v>0.09442</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.12512</v>
       </c>
     </row>
   </sheetData>
